--- a/Config/Table/xlsx/Localization.xlsx
+++ b/Config/Table/xlsx/Localization.xlsx
@@ -1244,6 +1244,7 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
+    <col min="2" max="2" width="27.125" customWidth="1"/>
     <col min="3" max="3" width="35.625" customWidth="1"/>
     <col min="4" max="4" width="55.625" customWidth="1"/>
   </cols>
